--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -462,6 +462,11 @@
           <t>param1</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -523,29 +528,12 @@
 3.材料</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>0.不可叠加
 1.可叠加</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -1,34 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F1C9B5-63F1-4C2B-99BD-9A28229BC381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>stackable</t>
+  </si>
+  <si>
+    <t>tip</t>
+  </si>
+  <si>
+    <t>func</t>
+  </si>
+  <si>
+    <t>param1</t>
+  </si>
+  <si>
+    <t>##备注</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>list#sep=|#,int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>物品ID</t>
+  </si>
+  <si>
+    <t>物品类型</t>
+  </si>
+  <si>
+    <t>物品名称</t>
+  </si>
+  <si>
+    <t>物品图标</t>
+  </si>
+  <si>
+    <t>是否可叠加</t>
+  </si>
+  <si>
+    <t>物品文本说明</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>参数1</t>
+  </si>
+  <si>
+    <t>金闪闪</t>
+  </si>
+  <si>
+    <t>拳王的牙齿</t>
+  </si>
+  <si>
+    <t>一口好牙</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.不可叠加
+1.可叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.可食用物品
+2.战斗内消耗品
+3.使用后获得BUFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>childtype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.(1.头2.胸3.手4.腿)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钱币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里的数字代表物品价值
+不填就是不可交易</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一堆烂牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打人用的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一嘴牙全让人打爆了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛顿最严厉的父亲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>万有引力果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0|1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.虚拟物品，不在背包显示
+2.剧情道具
+3.消耗品
+4.装备
+5.垃圾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +236,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,229 +542,273 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="25.25" customWidth="1"/>
+    <col min="4" max="4" width="24.25" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="10" max="10" width="23.375" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>stackable</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tip</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>func</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>param1</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>##备注</t>
-        </is>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>list#sep=|#,int</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1.虚拟物品
-2.剧情道具
-3.材料</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.不可叠加
-1.可叠加</t>
-        </is>
+    <row r="3" spans="1:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>物品ID</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>物品类型</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>物品名称</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>物品图标</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>是否可叠加</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>物品文本说明</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>参数1</t>
-        </is>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="n">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>钱币</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>金闪闪</t>
-        </is>
+      <c r="I5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>2</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>拳王的牙齿</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>一口好牙</t>
-        </is>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F1C9B5-63F1-4C2B-99BD-9A28229BC381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA081FC-E20B-4427-A873-106DAFE4CA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -193,6 +193,50 @@
 3.消耗品
 4.装备
 5.垃圾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑似大粪的钥匙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厕所钥匙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通假牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王钢牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石头拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑕疵假牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一口烂牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下手很重的拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卵用没有的拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通牙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -543,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -807,6 +851,126 @@
         <v>45</v>
       </c>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA081FC-E20B-4427-A873-106DAFE4CA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53712283-BE43-4BB0-818C-E75120230B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53712283-BE43-4BB0-818C-E75120230B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566A6B00-086A-4245-828F-E062CB2FA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,10 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>49</v>
@@ -896,7 +899,10 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
@@ -916,7 +922,10 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
       </c>
       <c r="E13" t="s">
         <v>51</v>
@@ -936,7 +945,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
       </c>
       <c r="E14" t="s">
         <v>52</v>
@@ -956,7 +968,10 @@
         <v>11</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
       </c>
       <c r="E15" t="s">
         <v>53</v>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566A6B00-086A-4245-828F-E062CB2FA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A2C250-77CA-4C2F-A4F0-593B070C0884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>金闪闪</t>
-  </si>
-  <si>
-    <t>拳王的牙齿</t>
   </si>
   <si>
     <t>一口好牙</t>
@@ -135,10 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>钱币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bool</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -153,38 +146,6 @@
   <si>
     <t>这里的数字代表物品价值
 不填就是不可交易</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一堆烂牙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打人用的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一嘴牙全让人打爆了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛顿最严厉的父亲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1|3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>万有引力果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0|1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -237,6 +198,10 @@
   </si>
   <si>
     <t>普通牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牙齿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -614,7 +579,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -623,7 +588,7 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -652,7 +617,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -661,10 +626,10 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
         <v>12</v>
@@ -682,20 +647,20 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
@@ -709,7 +674,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -718,7 +683,7 @@
         <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
@@ -741,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -761,19 +726,16 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
@@ -784,10 +746,10 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -796,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.15">
@@ -804,22 +766,22 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.15">
@@ -827,28 +789,22 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.15">
@@ -856,10 +812,13 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -868,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.15">
@@ -882,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -891,99 +850,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B12">
-        <v>8</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B13">
-        <v>9</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F13">
-        <v>9</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15">
-        <v>11</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A2C250-77CA-4C2F-A4F0-593B070C0884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAFDD04-D1D4-460A-B702-2AF9922FDFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>金闪闪</t>
   </si>
   <si>
-    <t>一口好牙</t>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -157,10 +154,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>疑似大粪的钥匙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>厕所钥匙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,31 +170,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>石头拳套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>瑕疵假牙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>一口烂牙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下手很重的拳套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卵用没有的拳套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通牙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>牙齿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从厕所里掏出来的东西，一般认为这是一把钥匙，至于它&lt;color=red&gt;真的是什么&lt;/color&gt;，谁在乎呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一套普通的牙，咬啤酒瓶弄掉过几个角，整体黄不拉几的，不过没人能否认这确实是一套牙。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通的拳套，只存在象征性的意义，不要想拳套能为你做些什么，要问你能为拳套&lt;color=red&gt;做些什么&lt;/color&gt;。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一口好牙，一位伟大的拳王曾经用它咬掉过很多人的耳朵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石膏拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砸在脸上的感觉像是大卡车的冲撞，在他的抚摸下下没有人能够不被&lt;color=red&gt;哄睡&lt;/color&gt;。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑似牙齿的东西，它已经太老以至于跟不上时代了，就连蛀虫都嫌弃这是套老破小。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +564,7 @@
     <col min="6" max="6" width="13.5" customWidth="1"/>
     <col min="7" max="7" width="16.75" customWidth="1"/>
     <col min="8" max="8" width="12.75" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.375" customWidth="1"/>
     <col min="11" max="11" width="12.625" customWidth="1"/>
   </cols>
@@ -579,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -588,12 +589,12 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" t="s">
@@ -617,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -626,12 +627,12 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J2" t="s">
@@ -647,20 +648,20 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
@@ -674,7 +675,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -683,12 +684,12 @@
         <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="J4" t="s">
@@ -706,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -714,11 +715,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B6">
         <v>2</v>
       </c>
@@ -726,7 +727,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -734,11 +735,11 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B7">
         <v>3</v>
       </c>
@@ -749,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -757,11 +758,11 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="I7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B8">
         <v>4</v>
       </c>
@@ -772,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -780,11 +781,11 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="I8" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="27" x14ac:dyDescent="0.15">
       <c r="B9">
         <v>5</v>
       </c>
@@ -795,7 +796,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -803,11 +804,11 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="I9" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B10">
         <v>6</v>
       </c>
@@ -818,7 +819,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -826,11 +827,11 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="I10" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B11">
         <v>7</v>
       </c>
@@ -841,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -849,8 +850,8 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
-        <v>44</v>
+      <c r="I11" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAFDD04-D1D4-460A-B702-2AF9922FDFA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FABC36-BA16-4AF6-8AC1-055A3FECFFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FABC36-BA16-4AF6-8AC1-055A3FECFFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BE3C41-FBC5-4D29-804E-BD7C2D4D3AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -203,6 +203,10 @@
   </si>
   <si>
     <t>疑似牙齿的东西，它已经太老以至于跟不上时代了，就连蛀虫都嫌弃这是套老破小。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验值+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -854,6 +858,23 @@
         <v>48</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>##备注</t>
+          <t>battletip</t>
         </is>
       </c>
     </row>
@@ -552,6 +552,11 @@
         </is>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -598,6 +603,11 @@
 3.使用后获得BUFF</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>物品战斗使用时显示的效果说明</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -653,6 +663,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>参数1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>物品战斗使用时详情</t>
         </is>
       </c>
     </row>
@@ -679,6 +694,11 @@
           <t>金闪闪</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40.5" customHeight="1">
       <c r="B6" t="n">
@@ -703,6 +723,11 @@
           <t>从厕所里掏出来的东西，一般认为这是一把钥匙，至于它&lt;color=red&gt;真的是什么&lt;/color&gt;，谁在乎呢？</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40.5" customHeight="1">
       <c r="B7" t="n">
@@ -735,6 +760,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
       <c r="B8" t="n">
@@ -767,6 +797,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="B9" t="n">
@@ -799,6 +834,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
       <c r="B10" t="n">
@@ -831,6 +871,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40.5" customHeight="1">
       <c r="B11" t="n">
@@ -863,6 +908,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="n">
@@ -881,6 +931,11 @@
       </c>
       <c r="H12" t="n">
         <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>战斗详情：待配置</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6B4DEA-F3B1-4BFE-B726-782E1F2517AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFEC702-BDC4-41C7-B641-12DF0541567F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -221,6 +221,30 @@
   </si>
   <si>
     <t>每一拳砸下去，飞溅的水珠都像在替对手喊疼，而你自己也分不清，那是汗水、自来水，还是昨夜梦见自己输掉比赛时偷流的眼泪。\n他妈的耍赖，他妈的用力打每一个人！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鞭炮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸！爆炸！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绷带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗！治疗！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸毁一切！\n炸掉敌人10点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包扎伤口\n为选中的友方单位回复10点生命值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -264,11 +288,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -571,100 +596,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="2" width="13.375" customWidth="1"/>
-    <col min="3" max="3" width="25.25" customWidth="1"/>
-    <col min="4" max="4" width="24.25" customWidth="1"/>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="16.75" customWidth="1"/>
-    <col min="8" max="8" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.375" customWidth="1"/>
-    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="23.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="84" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="1"/>
@@ -684,283 +710,335 @@
       <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B5">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>4</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>3</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8">
+      <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>3</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>4</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9">
+      <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>5</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10">
+      <c r="B10" s="2">
         <v>6</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>3</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>6</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11">
+      <c r="B11" s="2">
         <v>7</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>4</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>7</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="B12">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>8</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
-      <c r="B13">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>6</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>2</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>11</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="2" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="2">
+        <v>11</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="2">
+        <v>11</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFEC702-BDC4-41C7-B641-12DF0541567F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7CED98-DDB7-4ADB-8F46-61633D175D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -92,11 +92,6 @@
 1.可叠加</t>
   </si>
   <si>
-    <t>1.可食用物品
-2.战斗内消耗品
-3.使用后获得BUFF</t>
-  </si>
-  <si>
     <t>物品战斗使用时显示的效果说明</t>
   </si>
   <si>
@@ -200,6 +195,42 @@
   </si>
   <si>
     <t>套狗队电话号码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>套狗队的联系方式，朋克城外一切动物的克星。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>又遇到猫了？没问题！遇到狗了？没问题！遇到变异动物了？那更没问题了！我们天生就是他妈干这个的！马上到那野狗楼下！我爱生活！\n战斗中为你解决字面意义上的野狗敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每一拳砸下去，飞溅的水珠都像在替对手喊疼，而你自己也分不清，那是汗水、自来水，还是昨夜梦见自己输掉比赛时偷流的眼泪。\n他妈的耍赖，他妈的用力打每一个人！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鞭炮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸！爆炸！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绷带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗！治疗！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸毁一切！\n炸掉敌人10点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包扎伤口\n为选中的友方单位回复10点生命值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -207,44 +238,64 @@
 2.剧情道具
 3.消耗品
 4.装备
-5.垃圾
-6.战斗中可使用道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>套狗队的联系方式，朋克城外一切动物的克星。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>又遇到猫了？没问题！遇到狗了？没问题！遇到变异动物了？那更没问题了！我们天生就是他妈干这个的！马上到那野狗楼下！我爱生活！\n战斗中为你解决字面意义上的野狗敌人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每一拳砸下去，飞溅的水珠都像在替对手喊疼，而你自己也分不清，那是汗水、自来水，还是昨夜梦见自己输掉比赛时偷流的眼泪。\n他妈的耍赖，他妈的用力打每一个人！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鞭炮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爆炸！爆炸！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绷带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>治疗！治疗！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>炸毁一切！\n炸掉敌人10点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>包扎伤口\n为选中的友方单位回复10点生命值</t>
+5.垃圾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>param2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list#sep=|#,int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责管理所有物品功能
+1.战斗内对己方使用
+2.战斗内对敌方使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>param3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应物品的范围
+使用小键盘九宫格对应形状，5为选中本体
+1|2|3 即为一行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|5|8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5|29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成了多少伤害/治疗/对应BUFF的id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对某种范围内敌人造成Y效果
+多个效果就竖杠隔开
+Y1|Y2
+1.一次性造成X（对应参数3）治疗效果
+2.一次性造成X（对应参数3）物理伤害效果
+3.给目标增加BUFF（id对应buff表）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -288,12 +339,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -596,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -608,12 +665,14 @@
     <col min="7" max="7" width="16.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="34.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.625" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="10" max="10" width="23.375" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.75" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -641,17 +700,23 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -679,23 +744,29 @@
       <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:14" ht="126" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
@@ -707,52 +778,67 @@
       <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -760,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -769,13 +855,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -783,7 +869,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2">
         <v>2</v>
@@ -792,13 +878,13 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>38</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -809,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
@@ -818,16 +904,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N7" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -838,7 +924,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
@@ -847,16 +933,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N8" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -867,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
@@ -876,27 +962,27 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N9" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
         <v>6</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
@@ -905,16 +991,16 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -925,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2">
         <v>7</v>
@@ -934,16 +1020,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="N11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -951,7 +1037,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="2">
         <v>8</v>
@@ -959,19 +1045,19 @@
       <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="27" x14ac:dyDescent="0.15">
+      <c r="N12" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="27" x14ac:dyDescent="0.15">
       <c r="B13" s="2">
         <v>11</v>
       </c>
       <c r="C13" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -980,24 +1066,24 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" s="2">
+        <v>56</v>
+      </c>
+      <c r="K13" s="3">
         <v>11</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="N13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B14" s="2">
         <v>12</v>
       </c>
       <c r="C14" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F14" s="2">
         <v>2</v>
@@ -1006,24 +1092,33 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="2">
-        <v>11</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="3">
+        <v>5</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
         <v>13</v>
       </c>
       <c r="C15" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F15" s="2">
         <v>2</v>
@@ -1032,13 +1127,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M15" s="3">
+        <v>10</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="K15" s="2">
-        <v>11</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/item.xlsx
+++ b/DataTables/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7CED98-DDB7-4ADB-8F46-61633D175D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93747AC0-8EEB-42B7-8919-D9C9D001E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -101,9 +101,6 @@
     <t>物品ID</t>
   </si>
   <si>
-    <t>物品类型</t>
-  </si>
-  <si>
     <t>子类型</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
   </si>
   <si>
     <t>厕所钥匙</t>
-  </si>
-  <si>
-    <t>从厕所里掏出来的东西，一般认为这是一把钥匙，至于它&lt;color=red&gt;真的是什么&lt;/color&gt;，谁在乎呢？</t>
   </si>
   <si>
     <t>普通假牙</t>
@@ -296,6 +290,71 @@
 1.一次性造成X（对应参数3）治疗效果
 2.一次性造成X（对应参数3）物理伤害效果
 3.给目标增加BUFF（id对应buff表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品类型
+1-100为虚拟道具和测试道具
+1000-1999是第一章道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试道具占位</t>
+  </si>
+  <si>
+    <t>测试道具占位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从厕所里掏出来的东西，一般认为这是一把钥匙，至于它&lt;color=red&gt;真的是什么&lt;/color&gt;，谁在乎呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你经历了无数的艰辛和辛酸淘到的东西，是&lt;color=red&gt;某个档案柜的钥匙&lt;/color&gt;，或者说它最好是一把钥匙。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厕所钥匙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练的档案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>九龙药剂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通假牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳王钢牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三个愿望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石膏拳套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外星人脑子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑕疵假牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医生大脑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -319,12 +378,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -339,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -350,6 +415,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" style="2" customWidth="1"/>
@@ -707,10 +779,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>11</v>
@@ -745,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>16</v>
@@ -766,7 +838,7 @@
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
@@ -779,63 +851,63 @@
         <v>20</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
@@ -846,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
@@ -855,10 +927,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -869,7 +941,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2">
         <v>2</v>
@@ -878,10 +950,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -895,7 +967,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
@@ -904,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -924,7 +996,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
@@ -933,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.15">
@@ -953,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
@@ -962,13 +1034,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -982,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
@@ -991,13 +1063,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
@@ -1011,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2">
         <v>7</v>
@@ -1020,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.15">
@@ -1037,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F12" s="2">
         <v>8</v>
@@ -1046,7 +1118,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="27" x14ac:dyDescent="0.15">
@@ -1057,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -1066,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K13" s="3">
         <v>11</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.15">
@@ -1083,7 +1155,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F14" s="2">
         <v>2</v>
@@ -1092,22 +1164,22 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J14" s="3">
         <v>2</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L14" s="3">
         <v>5</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.15">
@@ -1118,7 +1190,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15" s="2">
         <v>2</v>
@@ -1127,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J15" s="3">
         <v>1</v>
@@ -1136,13 +1208,274 @@
         <v>1</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M15" s="3">
         <v>10</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="5">
+        <v>100</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="N16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="B17" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1001</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B18" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1002</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B19" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1003</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B20" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1004</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B21" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1005</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B22" s="2">
+        <v>1006</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1006</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B23" s="2">
+        <v>1007</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1007</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B24" s="2">
+        <v>1008</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1008</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B25" s="2">
+        <v>1009</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1009</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B26" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C26" s="2">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1010</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B27" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1011</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
